--- a/tables/Students.xlsx
+++ b/tables/Students.xlsx
@@ -1,40 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Работа\ФСиР\Кураторство\Встреча с куратором 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alina_kotya\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40D2D2D-40A7-43D3-BAF7-85AFB317F1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA707329-9850-4D24-ABA9-369A5E9AAB2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ПИ" sheetId="5" r:id="rId1"/>
-    <sheet name="Списки групп РПО" sheetId="8" r:id="rId2"/>
-    <sheet name="Списки групп Дизайн" sheetId="7" r:id="rId3"/>
-    <sheet name="УП" sheetId="6" r:id="rId4"/>
-    <sheet name="РиСО" sheetId="3" r:id="rId5"/>
-    <sheet name="Туризм" sheetId="4" r:id="rId6"/>
-    <sheet name="Сервис" sheetId="2" r:id="rId7"/>
+    <sheet name="РПО 14121" sheetId="8" r:id="rId2"/>
+    <sheet name="РПО 14123" sheetId="10" r:id="rId3"/>
+    <sheet name="Дизайн 14122" sheetId="7" r:id="rId4"/>
+    <sheet name="Дизайн 14124" sheetId="9" r:id="rId5"/>
+    <sheet name="УП" sheetId="6" r:id="rId6"/>
+    <sheet name="РиСО" sheetId="3" r:id="rId7"/>
+    <sheet name="Туризм" sheetId="4" r:id="rId8"/>
+    <sheet name="Сервис" sheetId="2" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ПИ!$A$1:$K$74</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">ПИ!$A$3:$L$74</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">РиСО!$A$1:$I$47</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">Сервис!$A$1:$L$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">Туризм!$A$3:$L$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">УП!$A$1:$L$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">ПИ!$A$1:$L$72</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">РиСО!$A$1:$I$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">Сервис!$A$1:$L$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">Туризм!$A$1:$L$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">УП!$A$1:$L$14</definedName>
   </definedNames>
   <calcPr calcId="124519" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="186">
   <si>
     <t>№ п/п</t>
   </si>
@@ -588,29 +589,17 @@
     <t>100% 53мин</t>
   </si>
   <si>
-    <t>Группа 14122</t>
-  </si>
-  <si>
-    <t>Группа 14124</t>
-  </si>
-  <si>
     <t>Жовтый Иван Антонович</t>
   </si>
   <si>
     <t>Алексеев Николай Евгеньевич</t>
-  </si>
-  <si>
-    <t>Группа 14121</t>
-  </si>
-  <si>
-    <t>Группа 14123</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <name val="Arial"/>
@@ -643,19 +632,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -673,22 +649,8 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -701,14 +663,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="21">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -878,19 +834,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -964,11 +907,144 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1003,9 +1079,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1028,7 +1101,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1037,14 +1110,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="5"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1054,14 +1126,16 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1070,10 +1144,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1100,7 +1174,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1109,19 +1183,37 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1139,53 +1231,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1498,7 +1555,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:AI74"/>
+  <dimension ref="A1:AI72"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="7" customWidth="1"/>
@@ -1506,106 +1563,114 @@
     <col min="3" max="8" width="10.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="11" style="1" customWidth="1"/>
     <col min="10" max="10" width="22.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="20.28515625" style="22" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" style="21" customWidth="1"/>
     <col min="12" max="14" width="0.140625" style="1" customWidth="1"/>
     <col min="15" max="15" width="0.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7"/>
-      <c r="B1"/>
-      <c r="C1"/>
-      <c r="D1"/>
-      <c r="E1"/>
-      <c r="F1"/>
-      <c r="G1"/>
-      <c r="H1"/>
-      <c r="I1"/>
-      <c r="J1"/>
-      <c r="K1" s="22"/>
-      <c r="L1"/>
-      <c r="M1"/>
-      <c r="N1"/>
-      <c r="O1"/>
+    <row r="1" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="13"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="K1" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
     </row>
     <row r="2" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="L2"/>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
     </row>
     <row r="3" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="14"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="35" t="s">
-        <v>166</v>
-      </c>
-      <c r="K3" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
+      <c r="A3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
     </row>
     <row r="4" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="14"/>
-      <c r="B4" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
+      <c r="A4" s="10">
+        <v>1</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="19">
+        <v>24</v>
+      </c>
     </row>
     <row r="5" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-    </row>
-    <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="10">
+        <v>2</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="K5" s="19">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="C6" s="43"/>
       <c r="D6" s="43"/>
@@ -1614,17 +1679,17 @@
       <c r="G6" s="43"/>
       <c r="H6" s="43"/>
       <c r="I6" s="44"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="20">
+      <c r="J6" s="15"/>
+      <c r="K6" s="19">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="C7" s="43"/>
       <c r="D7" s="43"/>
@@ -1633,19 +1698,17 @@
       <c r="G7" s="43"/>
       <c r="H7" s="43"/>
       <c r="I7" s="44"/>
-      <c r="J7" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="K7" s="20">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J7" s="15"/>
+      <c r="K7" s="19">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C8" s="43"/>
       <c r="D8" s="43"/>
@@ -1654,17 +1717,19 @@
       <c r="G8" s="43"/>
       <c r="H8" s="43"/>
       <c r="I8" s="44"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="20">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J8" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="K8" s="19">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C9" s="43"/>
       <c r="D9" s="43"/>
@@ -1673,17 +1738,21 @@
       <c r="G9" s="43"/>
       <c r="H9" s="43"/>
       <c r="I9" s="44"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="20">
+      <c r="J9" s="15"/>
+      <c r="K9" s="19">
         <v>24</v>
       </c>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
     </row>
     <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="C10" s="43"/>
       <c r="D10" s="43"/>
@@ -1692,19 +1761,19 @@
       <c r="G10" s="43"/>
       <c r="H10" s="43"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="K10" s="20">
+      <c r="J10" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="K10" s="19">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="C11" s="43"/>
       <c r="D11" s="43"/>
@@ -1713,21 +1782,17 @@
       <c r="G11" s="43"/>
       <c r="H11" s="43"/>
       <c r="I11" s="44"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="20">
+      <c r="J11" s="15"/>
+      <c r="K11" s="19">
         <v>24</v>
       </c>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
     </row>
     <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>142</v>
+        <v>16</v>
       </c>
       <c r="C12" s="43"/>
       <c r="D12" s="43"/>
@@ -1736,19 +1801,19 @@
       <c r="G12" s="43"/>
       <c r="H12" s="43"/>
       <c r="I12" s="44"/>
-      <c r="J12" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="K12" s="20">
+      <c r="J12" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="K12" s="19">
         <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
@@ -1757,17 +1822,17 @@
       <c r="G13" s="43"/>
       <c r="H13" s="43"/>
       <c r="I13" s="44"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="20">
+      <c r="J13" s="15"/>
+      <c r="K13" s="19">
         <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C14" s="43"/>
       <c r="D14" s="43"/>
@@ -1776,19 +1841,17 @@
       <c r="G14" s="43"/>
       <c r="H14" s="43"/>
       <c r="I14" s="44"/>
-      <c r="J14" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="K14" s="20">
-        <v>22</v>
+      <c r="J14" s="15"/>
+      <c r="K14" s="19">
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="C15" s="43"/>
       <c r="D15" s="43"/>
@@ -1797,17 +1860,19 @@
       <c r="G15" s="43"/>
       <c r="H15" s="43"/>
       <c r="I15" s="44"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="20">
-        <v>24</v>
+      <c r="J15" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="K15" s="19">
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="C16" s="43"/>
       <c r="D16" s="43"/>
@@ -1816,17 +1881,17 @@
       <c r="G16" s="43"/>
       <c r="H16" s="43"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="20">
+      <c r="J16" s="15"/>
+      <c r="K16" s="19">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="43"/>
@@ -1835,19 +1900,17 @@
       <c r="G17" s="43"/>
       <c r="H17" s="43"/>
       <c r="I17" s="44"/>
-      <c r="J17" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="K17" s="20">
-        <v>22</v>
+      <c r="J17" s="15"/>
+      <c r="K17" s="19">
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C18" s="43"/>
       <c r="D18" s="43"/>
@@ -1856,17 +1919,19 @@
       <c r="G18" s="43"/>
       <c r="H18" s="43"/>
       <c r="I18" s="44"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="20">
-        <v>24</v>
+      <c r="J18" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="K18" s="19">
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
@@ -1875,17 +1940,19 @@
       <c r="G19" s="43"/>
       <c r="H19" s="43"/>
       <c r="I19" s="44"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="20">
-        <v>24</v>
+      <c r="J19" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="K19" s="19">
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="43"/>
@@ -1894,19 +1961,19 @@
       <c r="G20" s="43"/>
       <c r="H20" s="43"/>
       <c r="I20" s="44"/>
-      <c r="J20" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="K20" s="20">
+      <c r="J20" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="K20" s="19">
         <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C21" s="43"/>
       <c r="D21" s="43"/>
@@ -1915,19 +1982,19 @@
       <c r="G21" s="43"/>
       <c r="H21" s="43"/>
       <c r="I21" s="44"/>
-      <c r="J21" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="K21" s="20">
+      <c r="J21" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="K21" s="19">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="C22" s="43"/>
       <c r="D22" s="43"/>
@@ -1936,19 +2003,17 @@
       <c r="G22" s="43"/>
       <c r="H22" s="43"/>
       <c r="I22" s="44"/>
-      <c r="J22" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="K22" s="20">
-        <v>22</v>
+      <c r="J22" s="20"/>
+      <c r="K22" s="19">
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C23" s="43"/>
       <c r="D23" s="43"/>
@@ -1957,80 +2022,99 @@
       <c r="G23" s="43"/>
       <c r="H23" s="43"/>
       <c r="I23" s="44"/>
-      <c r="J23" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="K23" s="20">
+      <c r="J23" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="K23" s="19">
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10">
-        <v>19</v>
-      </c>
-      <c r="B24" s="43" t="s">
-        <v>155</v>
-      </c>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="20">
-        <v>24</v>
+        <v>21</v>
+      </c>
+      <c r="B24" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="K24" s="19">
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="10">
-        <v>20</v>
-      </c>
-      <c r="B25" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="43"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="K25" s="20">
         <v>22</v>
+      </c>
+      <c r="B25" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="19">
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
-        <v>21</v>
-      </c>
-      <c r="B26" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="48"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="K26" s="20">
+        <v>23</v>
+      </c>
+      <c r="B26" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="K26" s="19">
         <v>22</v>
       </c>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="1"/>
+      <c r="AD26" s="1"/>
+      <c r="AE26" s="1"/>
+      <c r="AF26" s="1"/>
+      <c r="AG26" s="1"/>
+      <c r="AH26" s="1"/>
+      <c r="AI26" s="1"/>
     </row>
     <row r="27" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C27" s="41"/>
       <c r="D27" s="41"/>
@@ -2039,17 +2123,38 @@
       <c r="G27" s="41"/>
       <c r="H27" s="41"/>
       <c r="I27" s="42"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="20">
-        <v>24</v>
-      </c>
+      <c r="J27" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="K27" s="19">
+        <v>22</v>
+      </c>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="3"/>
+      <c r="Y27" s="3"/>
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
+      <c r="AB27" s="3"/>
+      <c r="AC27" s="3"/>
+      <c r="AD27" s="3"/>
+      <c r="AE27" s="3"/>
+      <c r="AF27" s="3"/>
+      <c r="AG27" s="3"/>
+      <c r="AH27" s="3"/>
+      <c r="AI27" s="3"/>
     </row>
     <row r="28" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B28" s="41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C28" s="41"/>
       <c r="D28" s="41"/>
@@ -2058,38 +2163,23 @@
       <c r="G28" s="41"/>
       <c r="H28" s="41"/>
       <c r="I28" s="42"/>
-      <c r="J28" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="K28" s="20">
+      <c r="J28" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="K28" s="19">
         <v>22</v>
       </c>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-      <c r="Z28" s="1"/>
-      <c r="AA28" s="1"/>
-      <c r="AB28" s="1"/>
-      <c r="AC28" s="1"/>
-      <c r="AD28" s="1"/>
-      <c r="AE28" s="1"/>
-      <c r="AF28" s="1"/>
-      <c r="AG28" s="1"/>
-      <c r="AH28" s="1"/>
-      <c r="AI28" s="1"/>
     </row>
     <row r="29" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B29" s="41" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C29" s="41"/>
       <c r="D29" s="41"/>
@@ -2098,38 +2188,19 @@
       <c r="G29" s="41"/>
       <c r="H29" s="41"/>
       <c r="I29" s="42"/>
-      <c r="J29" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="K29" s="20">
+      <c r="J29" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="K29" s="19">
         <v>22</v>
       </c>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="U29" s="3"/>
-      <c r="V29" s="3"/>
-      <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
-      <c r="Y29" s="3"/>
-      <c r="Z29" s="3"/>
-      <c r="AA29" s="3"/>
-      <c r="AB29" s="3"/>
-      <c r="AC29" s="3"/>
-      <c r="AD29" s="3"/>
-      <c r="AE29" s="3"/>
-      <c r="AF29" s="3"/>
-      <c r="AG29" s="3"/>
-      <c r="AH29" s="3"/>
-      <c r="AI29" s="3"/>
     </row>
     <row r="30" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B30" s="41" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C30" s="41"/>
       <c r="D30" s="41"/>
@@ -2138,23 +2209,19 @@
       <c r="G30" s="41"/>
       <c r="H30" s="41"/>
       <c r="I30" s="42"/>
-      <c r="J30" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="K30" s="20">
+      <c r="J30" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="K30" s="19">
         <v>22</v>
       </c>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
     </row>
     <row r="31" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B31" s="41" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C31" s="41"/>
       <c r="D31" s="41"/>
@@ -2163,19 +2230,17 @@
       <c r="G31" s="41"/>
       <c r="H31" s="41"/>
       <c r="I31" s="42"/>
-      <c r="J31" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="K31" s="20">
-        <v>22</v>
+      <c r="J31" s="15"/>
+      <c r="K31" s="19">
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B32" s="41" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C32" s="41"/>
       <c r="D32" s="41"/>
@@ -2184,19 +2249,17 @@
       <c r="G32" s="41"/>
       <c r="H32" s="41"/>
       <c r="I32" s="42"/>
-      <c r="J32" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="K32" s="20">
-        <v>22</v>
+      <c r="J32" s="15"/>
+      <c r="K32" s="19">
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B33" s="41" t="s">
-        <v>10</v>
+        <v>143</v>
       </c>
       <c r="C33" s="41"/>
       <c r="D33" s="41"/>
@@ -2205,17 +2268,23 @@
       <c r="G33" s="41"/>
       <c r="H33" s="41"/>
       <c r="I33" s="42"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="20">
-        <v>24</v>
-      </c>
+      <c r="J33" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="K33" s="19">
+        <v>22</v>
+      </c>
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33"/>
     </row>
     <row r="34" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B34" s="41" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="C34" s="41"/>
       <c r="D34" s="41"/>
@@ -2225,16 +2294,20 @@
       <c r="H34" s="41"/>
       <c r="I34" s="42"/>
       <c r="J34" s="16"/>
-      <c r="K34" s="20">
+      <c r="K34" s="19">
         <v>24</v>
       </c>
-    </row>
-    <row r="35" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+    </row>
+    <row r="35" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B35" s="41" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="C35" s="41"/>
       <c r="D35" s="41"/>
@@ -2243,23 +2316,21 @@
       <c r="G35" s="41"/>
       <c r="H35" s="41"/>
       <c r="I35" s="42"/>
-      <c r="J35" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="K35" s="20">
-        <v>22</v>
-      </c>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="22">
+        <v>24</v>
+      </c>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
     </row>
     <row r="36" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B36" s="41" t="s">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="C36" s="41"/>
       <c r="D36" s="41"/>
@@ -2268,21 +2339,23 @@
       <c r="G36" s="41"/>
       <c r="H36" s="41"/>
       <c r="I36" s="42"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="20">
-        <v>24</v>
+      <c r="J36" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="K36" s="19">
+        <v>22</v>
       </c>
       <c r="L36"/>
       <c r="M36"/>
       <c r="N36"/>
       <c r="O36"/>
     </row>
-    <row r="37" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B37" s="41" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="C37" s="41"/>
       <c r="D37" s="41"/>
@@ -2291,21 +2364,21 @@
       <c r="G37" s="41"/>
       <c r="H37" s="41"/>
       <c r="I37" s="42"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="23">
+      <c r="J37" s="14"/>
+      <c r="K37" s="18">
         <v>24</v>
       </c>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
     </row>
     <row r="38" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B38" s="41" t="s">
-        <v>141</v>
+        <v>176</v>
       </c>
       <c r="C38" s="41"/>
       <c r="D38" s="41"/>
@@ -2314,124 +2387,118 @@
       <c r="G38" s="41"/>
       <c r="H38" s="41"/>
       <c r="I38" s="42"/>
-      <c r="J38" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="K38" s="20">
-        <v>22</v>
-      </c>
-      <c r="L38"/>
-      <c r="M38"/>
-      <c r="N38"/>
-      <c r="O38"/>
-    </row>
-    <row r="39" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="10">
-        <v>34</v>
-      </c>
-      <c r="B39" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="41"/>
-      <c r="I39" s="42"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="19">
+      <c r="J38" s="14"/>
+      <c r="K38" s="18">
         <v>24</v>
       </c>
-      <c r="L39"/>
-      <c r="M39"/>
-      <c r="N39"/>
-      <c r="O39"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
+      <c r="Y38" s="3"/>
+      <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
+      <c r="AB38" s="3"/>
+      <c r="AC38" s="3"/>
+      <c r="AD38" s="3"/>
+      <c r="AE38" s="3"/>
+      <c r="AF38" s="3"/>
+      <c r="AG38" s="3"/>
+      <c r="AH38" s="3"/>
+      <c r="AI38" s="3"/>
+    </row>
+    <row r="39" spans="1:35" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="8"/>
+      <c r="B39" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="C39" s="50"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="50"/>
+      <c r="I39" s="50"/>
+      <c r="J39" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="K39" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
     </row>
     <row r="40" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="10">
-        <v>35</v>
-      </c>
-      <c r="B40" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="41"/>
-      <c r="I40" s="42"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="19">
-        <v>24</v>
-      </c>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
-      <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="3"/>
-      <c r="AA40" s="3"/>
-      <c r="AB40" s="3"/>
-      <c r="AC40" s="3"/>
-      <c r="AD40" s="3"/>
-      <c r="AE40" s="3"/>
-      <c r="AF40" s="3"/>
-      <c r="AG40" s="3"/>
-      <c r="AH40" s="3"/>
-      <c r="AI40" s="3"/>
-    </row>
-    <row r="41" spans="1:35" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="8"/>
-      <c r="B41" s="50" t="s">
-        <v>140</v>
-      </c>
-      <c r="C41" s="50"/>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="50"/>
-      <c r="I41" s="50"/>
-      <c r="J41" s="35" t="s">
-        <v>166</v>
-      </c>
-      <c r="K41" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5"/>
+      <c r="A40" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="51"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="51"/>
+      <c r="G40" s="51"/>
+      <c r="H40" s="51"/>
+      <c r="I40" s="51"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
+    </row>
+    <row r="41" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="10">
+        <v>1</v>
+      </c>
+      <c r="B41" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="C41" s="38"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="38"/>
+      <c r="J41" s="29">
+        <v>11</v>
+      </c>
+      <c r="K41" s="19">
+        <v>23</v>
+      </c>
     </row>
     <row r="42" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" s="51"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="51"/>
-      <c r="H42" s="51"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="36"/>
-      <c r="K42" s="36"/>
+      <c r="A42" s="10">
+        <v>2</v>
+      </c>
+      <c r="B42" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="C42" s="38"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="38"/>
+      <c r="I42" s="39"/>
+      <c r="J42" s="29">
+        <v>11.2</v>
+      </c>
+      <c r="K42" s="19">
+        <v>23</v>
+      </c>
     </row>
     <row r="43" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C43" s="38"/>
       <c r="D43" s="38"/>
@@ -2440,19 +2507,19 @@
       <c r="G43" s="38"/>
       <c r="H43" s="38"/>
       <c r="I43" s="38"/>
-      <c r="J43" s="31">
-        <v>11</v>
-      </c>
-      <c r="K43" s="20">
+      <c r="J43" s="29">
         <v>23</v>
+      </c>
+      <c r="K43" s="19">
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>187</v>
+        <v>74</v>
       </c>
       <c r="C44" s="38"/>
       <c r="D44" s="38"/>
@@ -2460,20 +2527,20 @@
       <c r="F44" s="38"/>
       <c r="G44" s="38"/>
       <c r="H44" s="38"/>
-      <c r="I44" s="39"/>
-      <c r="J44" s="31">
-        <v>11.2</v>
-      </c>
-      <c r="K44" s="20">
-        <v>23</v>
+      <c r="I44" s="38"/>
+      <c r="J44" s="29">
+        <v>23.1</v>
+      </c>
+      <c r="K44" s="19">
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>144</v>
+        <v>65</v>
       </c>
       <c r="C45" s="38"/>
       <c r="D45" s="38"/>
@@ -2482,19 +2549,19 @@
       <c r="G45" s="38"/>
       <c r="H45" s="38"/>
       <c r="I45" s="38"/>
-      <c r="J45" s="31">
-        <v>23</v>
-      </c>
-      <c r="K45" s="20">
+      <c r="J45" s="29">
+        <v>23.2</v>
+      </c>
+      <c r="K45" s="19">
         <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C46" s="38"/>
       <c r="D46" s="38"/>
@@ -2504,18 +2571,18 @@
       <c r="H46" s="38"/>
       <c r="I46" s="38"/>
       <c r="J46" s="31">
-        <v>23.1</v>
-      </c>
-      <c r="K46" s="20">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="K46" s="19">
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B47" s="37" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C47" s="38"/>
       <c r="D47" s="38"/>
@@ -2524,19 +2591,39 @@
       <c r="G47" s="38"/>
       <c r="H47" s="38"/>
       <c r="I47" s="38"/>
-      <c r="J47" s="31">
-        <v>23.2</v>
-      </c>
-      <c r="K47" s="20">
+      <c r="J47" s="29">
+        <v>23.5</v>
+      </c>
+      <c r="K47" s="19">
         <v>21</v>
       </c>
-    </row>
-    <row r="48" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P47"/>
+      <c r="Q47"/>
+      <c r="R47"/>
+      <c r="S47"/>
+      <c r="T47"/>
+      <c r="U47"/>
+      <c r="V47"/>
+      <c r="W47"/>
+      <c r="X47"/>
+      <c r="Y47"/>
+      <c r="Z47"/>
+      <c r="AA47"/>
+      <c r="AB47"/>
+      <c r="AC47"/>
+      <c r="AD47"/>
+      <c r="AE47"/>
+      <c r="AF47"/>
+      <c r="AG47"/>
+      <c r="AH47"/>
+      <c r="AI47"/>
+    </row>
+    <row r="48" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B48" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48" s="38"/>
       <c r="D48" s="38"/>
@@ -2545,19 +2632,39 @@
       <c r="G48" s="38"/>
       <c r="H48" s="38"/>
       <c r="I48" s="38"/>
-      <c r="J48" s="33">
-        <v>34.299999999999997</v>
-      </c>
-      <c r="K48" s="20">
-        <v>21</v>
-      </c>
+      <c r="J48" s="29">
+        <v>5</v>
+      </c>
+      <c r="K48" s="19">
+        <v>23</v>
+      </c>
+      <c r="P48"/>
+      <c r="Q48"/>
+      <c r="R48"/>
+      <c r="S48"/>
+      <c r="T48"/>
+      <c r="U48"/>
+      <c r="V48"/>
+      <c r="W48"/>
+      <c r="X48"/>
+      <c r="Y48"/>
+      <c r="Z48"/>
+      <c r="AA48"/>
+      <c r="AB48"/>
+      <c r="AC48"/>
+      <c r="AD48"/>
+      <c r="AE48"/>
+      <c r="AF48"/>
+      <c r="AG48"/>
+      <c r="AH48"/>
+      <c r="AI48"/>
     </row>
     <row r="49" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B49" s="37" t="s">
-        <v>54</v>
+        <v>184</v>
       </c>
       <c r="C49" s="38"/>
       <c r="D49" s="38"/>
@@ -2565,11 +2672,11 @@
       <c r="F49" s="38"/>
       <c r="G49" s="38"/>
       <c r="H49" s="38"/>
-      <c r="I49" s="38"/>
-      <c r="J49" s="31">
-        <v>23.5</v>
-      </c>
-      <c r="K49" s="20">
+      <c r="I49" s="39"/>
+      <c r="J49" s="29">
+        <v>45</v>
+      </c>
+      <c r="K49" s="19">
         <v>21</v>
       </c>
       <c r="P49"/>
@@ -2595,10 +2702,10 @@
     </row>
     <row r="50" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B50" s="37" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C50" s="38"/>
       <c r="D50" s="38"/>
@@ -2607,11 +2714,11 @@
       <c r="G50" s="38"/>
       <c r="H50" s="38"/>
       <c r="I50" s="38"/>
-      <c r="J50" s="31">
-        <v>5</v>
-      </c>
-      <c r="K50" s="20">
-        <v>23</v>
+      <c r="J50" s="29">
+        <v>23.5</v>
+      </c>
+      <c r="K50" s="19">
+        <v>21</v>
       </c>
       <c r="P50"/>
       <c r="Q50"/>
@@ -2636,10 +2743,10 @@
     </row>
     <row r="51" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B51" s="37" t="s">
-        <v>186</v>
+        <v>129</v>
       </c>
       <c r="C51" s="38"/>
       <c r="D51" s="38"/>
@@ -2647,12 +2754,12 @@
       <c r="F51" s="38"/>
       <c r="G51" s="38"/>
       <c r="H51" s="38"/>
-      <c r="I51" s="39"/>
-      <c r="J51" s="31">
-        <v>45</v>
-      </c>
-      <c r="K51" s="20">
-        <v>21</v>
+      <c r="I51" s="38"/>
+      <c r="J51" s="29">
+        <v>11.1</v>
+      </c>
+      <c r="K51" s="19">
+        <v>23</v>
       </c>
       <c r="P51"/>
       <c r="Q51"/>
@@ -2677,10 +2784,10 @@
     </row>
     <row r="52" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B52" s="37" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C52" s="38"/>
       <c r="D52" s="38"/>
@@ -2689,10 +2796,10 @@
       <c r="G52" s="38"/>
       <c r="H52" s="38"/>
       <c r="I52" s="38"/>
-      <c r="J52" s="31">
+      <c r="J52" s="29">
         <v>23.5</v>
       </c>
-      <c r="K52" s="20">
+      <c r="K52" s="19">
         <v>21</v>
       </c>
       <c r="P52"/>
@@ -2718,10 +2825,10 @@
     </row>
     <row r="53" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B53" s="37" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="C53" s="38"/>
       <c r="D53" s="38"/>
@@ -2730,11 +2837,11 @@
       <c r="G53" s="38"/>
       <c r="H53" s="38"/>
       <c r="I53" s="38"/>
-      <c r="J53" s="31">
-        <v>11.1</v>
-      </c>
-      <c r="K53" s="20">
-        <v>23</v>
+      <c r="J53" s="29">
+        <v>23.2</v>
+      </c>
+      <c r="K53" s="19">
+        <v>21</v>
       </c>
       <c r="P53"/>
       <c r="Q53"/>
@@ -2759,10 +2866,10 @@
     </row>
     <row r="54" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B54" s="37" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C54" s="38"/>
       <c r="D54" s="38"/>
@@ -2771,11 +2878,11 @@
       <c r="G54" s="38"/>
       <c r="H54" s="38"/>
       <c r="I54" s="38"/>
-      <c r="J54" s="31">
-        <v>23.5</v>
-      </c>
-      <c r="K54" s="20">
-        <v>21</v>
+      <c r="J54" s="29">
+        <v>11.1</v>
+      </c>
+      <c r="K54" s="19">
+        <v>23</v>
       </c>
       <c r="P54"/>
       <c r="Q54"/>
@@ -2800,10 +2907,10 @@
     </row>
     <row r="55" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B55" s="37" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C55" s="38"/>
       <c r="D55" s="38"/>
@@ -2812,11 +2919,11 @@
       <c r="G55" s="38"/>
       <c r="H55" s="38"/>
       <c r="I55" s="38"/>
-      <c r="J55" s="31">
-        <v>23.2</v>
-      </c>
-      <c r="K55" s="20">
-        <v>21</v>
+      <c r="J55" s="29">
+        <v>11.2</v>
+      </c>
+      <c r="K55" s="19">
+        <v>23</v>
       </c>
       <c r="P55"/>
       <c r="Q55"/>
@@ -2841,10 +2948,10 @@
     </row>
     <row r="56" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B56" s="37" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C56" s="38"/>
       <c r="D56" s="38"/>
@@ -2853,10 +2960,10 @@
       <c r="G56" s="38"/>
       <c r="H56" s="38"/>
       <c r="I56" s="38"/>
-      <c r="J56" s="31">
+      <c r="J56" s="29">
         <v>11.1</v>
       </c>
-      <c r="K56" s="20">
+      <c r="K56" s="19">
         <v>23</v>
       </c>
       <c r="P56"/>
@@ -2882,10 +2989,10 @@
     </row>
     <row r="57" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B57" s="37" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="C57" s="38"/>
       <c r="D57" s="38"/>
@@ -2894,10 +3001,10 @@
       <c r="G57" s="38"/>
       <c r="H57" s="38"/>
       <c r="I57" s="38"/>
-      <c r="J57" s="31">
+      <c r="J57" s="29">
         <v>11.2</v>
       </c>
-      <c r="K57" s="20">
+      <c r="K57" s="19">
         <v>23</v>
       </c>
       <c r="P57"/>
@@ -2923,10 +3030,10 @@
     </row>
     <row r="58" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B58" s="37" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="C58" s="38"/>
       <c r="D58" s="38"/>
@@ -2935,10 +3042,10 @@
       <c r="G58" s="38"/>
       <c r="H58" s="38"/>
       <c r="I58" s="38"/>
-      <c r="J58" s="31">
-        <v>11.1</v>
-      </c>
-      <c r="K58" s="20">
+      <c r="J58" s="29">
+        <v>11.2</v>
+      </c>
+      <c r="K58" s="19">
         <v>23</v>
       </c>
       <c r="P58"/>
@@ -2964,10 +3071,10 @@
     </row>
     <row r="59" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B59" s="37" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="C59" s="38"/>
       <c r="D59" s="38"/>
@@ -2976,11 +3083,11 @@
       <c r="G59" s="38"/>
       <c r="H59" s="38"/>
       <c r="I59" s="38"/>
-      <c r="J59" s="31">
-        <v>11.2</v>
-      </c>
-      <c r="K59" s="20">
-        <v>23</v>
+      <c r="J59" s="29">
+        <v>23.1</v>
+      </c>
+      <c r="K59" s="19">
+        <v>21</v>
       </c>
       <c r="P59"/>
       <c r="Q59"/>
@@ -3005,10 +3112,10 @@
     </row>
     <row r="60" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B60" s="37" t="s">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="C60" s="38"/>
       <c r="D60" s="38"/>
@@ -3017,11 +3124,11 @@
       <c r="G60" s="38"/>
       <c r="H60" s="38"/>
       <c r="I60" s="38"/>
-      <c r="J60" s="31">
-        <v>11.2</v>
-      </c>
-      <c r="K60" s="20">
-        <v>23</v>
+      <c r="J60" s="29">
+        <v>23.1</v>
+      </c>
+      <c r="K60" s="19">
+        <v>21</v>
       </c>
       <c r="P60"/>
       <c r="Q60"/>
@@ -3046,10 +3153,10 @@
     </row>
     <row r="61" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B61" s="37" t="s">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="C61" s="38"/>
       <c r="D61" s="38"/>
@@ -3058,11 +3165,11 @@
       <c r="G61" s="38"/>
       <c r="H61" s="38"/>
       <c r="I61" s="38"/>
-      <c r="J61" s="31">
-        <v>23.1</v>
-      </c>
-      <c r="K61" s="20">
-        <v>21</v>
+      <c r="J61" s="29">
+        <v>11.2</v>
+      </c>
+      <c r="K61" s="19">
+        <v>23</v>
       </c>
       <c r="P61"/>
       <c r="Q61"/>
@@ -3087,10 +3194,10 @@
     </row>
     <row r="62" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B62" s="37" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C62" s="38"/>
       <c r="D62" s="38"/>
@@ -3099,11 +3206,11 @@
       <c r="G62" s="38"/>
       <c r="H62" s="38"/>
       <c r="I62" s="38"/>
-      <c r="J62" s="31">
-        <v>23.1</v>
-      </c>
-      <c r="K62" s="20">
-        <v>21</v>
+      <c r="J62" s="29">
+        <v>11.1</v>
+      </c>
+      <c r="K62" s="19">
+        <v>23</v>
       </c>
       <c r="P62"/>
       <c r="Q62"/>
@@ -3128,10 +3235,10 @@
     </row>
     <row r="63" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="10">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B63" s="37" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="C63" s="38"/>
       <c r="D63" s="38"/>
@@ -3140,10 +3247,10 @@
       <c r="G63" s="38"/>
       <c r="H63" s="38"/>
       <c r="I63" s="38"/>
-      <c r="J63" s="31">
-        <v>11.2</v>
-      </c>
-      <c r="K63" s="20">
+      <c r="J63" s="29">
+        <v>5</v>
+      </c>
+      <c r="K63" s="19">
         <v>23</v>
       </c>
       <c r="P63"/>
@@ -3167,12 +3274,12 @@
       <c r="AH63"/>
       <c r="AI63"/>
     </row>
-    <row r="64" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B64" s="37" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C64" s="38"/>
       <c r="D64" s="38"/>
@@ -3181,39 +3288,19 @@
       <c r="G64" s="38"/>
       <c r="H64" s="38"/>
       <c r="I64" s="38"/>
-      <c r="J64" s="31">
-        <v>11.1</v>
-      </c>
-      <c r="K64" s="20">
-        <v>23</v>
-      </c>
-      <c r="P64"/>
-      <c r="Q64"/>
-      <c r="R64"/>
-      <c r="S64"/>
-      <c r="T64"/>
-      <c r="U64"/>
-      <c r="V64"/>
-      <c r="W64"/>
-      <c r="X64"/>
-      <c r="Y64"/>
-      <c r="Z64"/>
-      <c r="AA64"/>
-      <c r="AB64"/>
-      <c r="AC64"/>
-      <c r="AD64"/>
-      <c r="AE64"/>
-      <c r="AF64"/>
-      <c r="AG64"/>
-      <c r="AH64"/>
-      <c r="AI64"/>
-    </row>
-    <row r="65" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J64" s="29">
+        <v>23.3</v>
+      </c>
+      <c r="K64" s="19">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B65" s="37" t="s">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="C65" s="38"/>
       <c r="D65" s="38"/>
@@ -3222,39 +3309,19 @@
       <c r="G65" s="38"/>
       <c r="H65" s="38"/>
       <c r="I65" s="38"/>
-      <c r="J65" s="31">
-        <v>5</v>
-      </c>
-      <c r="K65" s="20">
+      <c r="J65" s="29">
+        <v>11.2</v>
+      </c>
+      <c r="K65" s="19">
         <v>23</v>
       </c>
-      <c r="P65"/>
-      <c r="Q65"/>
-      <c r="R65"/>
-      <c r="S65"/>
-      <c r="T65"/>
-      <c r="U65"/>
-      <c r="V65"/>
-      <c r="W65"/>
-      <c r="X65"/>
-      <c r="Y65"/>
-      <c r="Z65"/>
-      <c r="AA65"/>
-      <c r="AB65"/>
-      <c r="AC65"/>
-      <c r="AD65"/>
-      <c r="AE65"/>
-      <c r="AF65"/>
-      <c r="AG65"/>
-      <c r="AH65"/>
-      <c r="AI65"/>
-    </row>
-    <row r="66" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="10">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B66" s="37" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C66" s="38"/>
       <c r="D66" s="38"/>
@@ -3263,19 +3330,19 @@
       <c r="G66" s="38"/>
       <c r="H66" s="38"/>
       <c r="I66" s="38"/>
-      <c r="J66" s="31">
-        <v>23.3</v>
-      </c>
-      <c r="K66" s="20">
+      <c r="J66" s="29">
+        <v>23.2</v>
+      </c>
+      <c r="K66" s="19">
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B67" s="37" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C67" s="38"/>
       <c r="D67" s="38"/>
@@ -3284,19 +3351,23 @@
       <c r="G67" s="38"/>
       <c r="H67" s="38"/>
       <c r="I67" s="38"/>
-      <c r="J67" s="31">
-        <v>11.2</v>
-      </c>
-      <c r="K67" s="20">
+      <c r="J67" s="29">
+        <v>11.8</v>
+      </c>
+      <c r="K67" s="19">
         <v>23</v>
       </c>
-    </row>
-    <row r="68" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B68" s="37" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C68" s="38"/>
       <c r="D68" s="38"/>
@@ -3305,19 +3376,17 @@
       <c r="G68" s="38"/>
       <c r="H68" s="38"/>
       <c r="I68" s="38"/>
-      <c r="J68" s="31">
-        <v>23.2</v>
-      </c>
-      <c r="K68" s="20">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="69" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J68" s="29"/>
+      <c r="K68" s="19">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B69" s="37" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C69" s="38"/>
       <c r="D69" s="38"/>
@@ -3326,23 +3395,19 @@
       <c r="G69" s="38"/>
       <c r="H69" s="38"/>
       <c r="I69" s="38"/>
-      <c r="J69" s="31">
-        <v>11.8</v>
-      </c>
-      <c r="K69" s="20">
-        <v>23</v>
-      </c>
-      <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J69" s="29">
+        <v>34</v>
+      </c>
+      <c r="K69" s="19">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="10">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B70" s="37" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C70" s="38"/>
       <c r="D70" s="38"/>
@@ -3351,17 +3416,19 @@
       <c r="G70" s="38"/>
       <c r="H70" s="38"/>
       <c r="I70" s="38"/>
-      <c r="J70" s="31"/>
-      <c r="K70" s="20">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="71" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J70" s="30">
+        <v>45</v>
+      </c>
+      <c r="K70" s="28">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="10">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B71" s="37" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C71" s="38"/>
       <c r="D71" s="38"/>
@@ -3370,19 +3437,19 @@
       <c r="G71" s="38"/>
       <c r="H71" s="38"/>
       <c r="I71" s="38"/>
-      <c r="J71" s="31">
-        <v>34</v>
-      </c>
-      <c r="K71" s="20">
+      <c r="J71" s="30">
+        <v>23.4</v>
+      </c>
+      <c r="K71" s="28">
         <v>21</v>
       </c>
     </row>
-    <row r="72" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B72" s="37" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C72" s="38"/>
       <c r="D72" s="38"/>
@@ -3391,57 +3458,16 @@
       <c r="G72" s="38"/>
       <c r="H72" s="38"/>
       <c r="I72" s="38"/>
-      <c r="J72" s="32">
-        <v>45</v>
-      </c>
-      <c r="K72" s="30">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="73" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="10">
-        <v>31</v>
-      </c>
-      <c r="B73" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="C73" s="38"/>
-      <c r="D73" s="38"/>
-      <c r="E73" s="38"/>
-      <c r="F73" s="38"/>
-      <c r="G73" s="38"/>
-      <c r="H73" s="38"/>
-      <c r="I73" s="38"/>
-      <c r="J73" s="32">
-        <v>23.4</v>
-      </c>
-      <c r="K73" s="30">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="74" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="10">
-        <v>32</v>
-      </c>
-      <c r="B74" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C74" s="38"/>
-      <c r="D74" s="38"/>
-      <c r="E74" s="38"/>
-      <c r="F74" s="38"/>
-      <c r="G74" s="38"/>
-      <c r="H74" s="38"/>
-      <c r="I74" s="38"/>
-      <c r="J74" s="31"/>
-      <c r="K74" s="20">
+      <c r="J72" s="29"/>
+      <c r="K72" s="19">
         <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K74" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="75">
-    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B61:I61"/>
+    <mergeCell ref="B62:I62"/>
     <mergeCell ref="B63:I63"/>
     <mergeCell ref="B64:I64"/>
     <mergeCell ref="B65:I65"/>
@@ -3451,10 +3477,10 @@
     <mergeCell ref="B69:I69"/>
     <mergeCell ref="B70:I70"/>
     <mergeCell ref="B71:I71"/>
-    <mergeCell ref="B72:I72"/>
-    <mergeCell ref="B73:I73"/>
-    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="B48:I48"/>
     <mergeCell ref="B50:I50"/>
+    <mergeCell ref="B51:I51"/>
     <mergeCell ref="B52:I52"/>
     <mergeCell ref="B53:I53"/>
     <mergeCell ref="B54:I54"/>
@@ -3463,27 +3489,27 @@
     <mergeCell ref="B57:I57"/>
     <mergeCell ref="B58:I58"/>
     <mergeCell ref="B59:I59"/>
-    <mergeCell ref="B60:I60"/>
-    <mergeCell ref="B61:I61"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="B41:I41"/>
-    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B33:I33"/>
     <mergeCell ref="B34:I34"/>
     <mergeCell ref="B35:I35"/>
     <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B37:I37"/>
     <mergeCell ref="B38:I38"/>
-    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="B41:I41"/>
     <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B44:I44"/>
     <mergeCell ref="B45:I45"/>
     <mergeCell ref="B46:I46"/>
-    <mergeCell ref="B47:I47"/>
-    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="B16:I16"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="B18:I18"/>
-    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B31:I31"/>
     <mergeCell ref="B20:I20"/>
-    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="B21:I21"/>
     <mergeCell ref="B22:I22"/>
     <mergeCell ref="B23:I23"/>
     <mergeCell ref="B24:I24"/>
@@ -3493,29 +3519,27 @@
     <mergeCell ref="B28:I28"/>
     <mergeCell ref="B29:I29"/>
     <mergeCell ref="B30:I30"/>
-    <mergeCell ref="B31:I31"/>
-    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="B14:I14"/>
-    <mergeCell ref="B15:I15"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="K41:K42"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="B39:I39"/>
-    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="K1:K3"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B19:I19"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B9:I9"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>
@@ -3523,30 +3547,73 @@
     <oddFooter>&amp;C&amp;"Arial,normal"&amp;8&amp;P из &amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="40" max="11" man="1"/>
+    <brk id="38" max="11" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5321A16A-A6AB-4BA0-BEBA-4A89D6886F2C}">
-  <dimension ref="A2:F41"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="25"/>
+    <col min="1" max="16384" width="9.140625" style="24"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B2" s="34" t="s">
-        <v>188</v>
-      </c>
+    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A1" s="25">
+        <v>1</v>
+      </c>
+      <c r="B1" s="52" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A2" s="25">
+        <v>2</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A3" s="25">
+        <v>3</v>
+      </c>
+      <c r="B3" s="52" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+    </row>
+    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="25">
+        <v>4</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
     </row>
     <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
-        <v>1</v>
+      <c r="A5" s="25">
+        <v>5</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="C5" s="52"/>
       <c r="D5" s="52"/>
@@ -3554,11 +3621,11 @@
       <c r="F5" s="52"/>
     </row>
     <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="26">
-        <v>2</v>
+      <c r="A6" s="25">
+        <v>6</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>74</v>
+        <v>184</v>
       </c>
       <c r="C6" s="52"/>
       <c r="D6" s="52"/>
@@ -3566,11 +3633,11 @@
       <c r="F6" s="52"/>
     </row>
     <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A7" s="26">
-        <v>3</v>
+      <c r="A7" s="25">
+        <v>7</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C7" s="52"/>
       <c r="D7" s="52"/>
@@ -3578,11 +3645,11 @@
       <c r="F7" s="52"/>
     </row>
     <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
-        <v>4</v>
+      <c r="A8" s="25">
+        <v>8</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" s="52"/>
       <c r="D8" s="52"/>
@@ -3590,11 +3657,11 @@
       <c r="F8" s="52"/>
     </row>
     <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A9" s="26">
-        <v>5</v>
+      <c r="A9" s="25">
+        <v>9</v>
       </c>
       <c r="B9" s="52" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C9" s="52"/>
       <c r="D9" s="52"/>
@@ -3602,11 +3669,11 @@
       <c r="F9" s="52"/>
     </row>
     <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A10" s="26">
-        <v>6</v>
+      <c r="A10" s="25">
+        <v>10</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>186</v>
+        <v>131</v>
       </c>
       <c r="C10" s="52"/>
       <c r="D10" s="52"/>
@@ -3614,11 +3681,11 @@
       <c r="F10" s="52"/>
     </row>
     <row r="11" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A11" s="26">
-        <v>7</v>
+      <c r="A11" s="25">
+        <v>11</v>
       </c>
       <c r="B11" s="52" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="C11" s="52"/>
       <c r="D11" s="52"/>
@@ -3626,11 +3693,11 @@
       <c r="F11" s="52"/>
     </row>
     <row r="12" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A12" s="26">
-        <v>8</v>
+      <c r="A12" s="25">
+        <v>12</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C12" s="52"/>
       <c r="D12" s="52"/>
@@ -3638,11 +3705,11 @@
       <c r="F12" s="52"/>
     </row>
     <row r="13" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A13" s="26">
-        <v>9</v>
+      <c r="A13" s="25">
+        <v>13</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="C13" s="52"/>
       <c r="D13" s="52"/>
@@ -3650,11 +3717,11 @@
       <c r="F13" s="52"/>
     </row>
     <row r="14" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A14" s="26">
-        <v>10</v>
+      <c r="A14" s="25">
+        <v>14</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>131</v>
+        <v>66</v>
       </c>
       <c r="C14" s="52"/>
       <c r="D14" s="52"/>
@@ -3662,11 +3729,11 @@
       <c r="F14" s="52"/>
     </row>
     <row r="15" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
-        <v>11</v>
+      <c r="A15" s="25">
+        <v>15</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C15" s="52"/>
       <c r="D15" s="52"/>
@@ -3674,265 +3741,725 @@
       <c r="F15" s="52"/>
     </row>
     <row r="16" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A16" s="26">
-        <v>12</v>
+      <c r="A16" s="25">
+        <v>16</v>
       </c>
       <c r="B16" s="52" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C16" s="52"/>
       <c r="D16" s="52"/>
       <c r="E16" s="52"/>
       <c r="F16" s="52"/>
     </row>
-    <row r="17" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A17" s="26">
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFEC9964-5A0F-4D53-8B12-1F97CBDF9F64}">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25">
+        <v>1</v>
+      </c>
+      <c r="B1" s="52" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+    </row>
+    <row r="2" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="25">
+        <v>2</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+    </row>
+    <row r="3" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="25">
+        <v>3</v>
+      </c>
+      <c r="B3" s="52" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+    </row>
+    <row r="4" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="25">
+        <v>4</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+    </row>
+    <row r="5" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="25">
+        <v>5</v>
+      </c>
+      <c r="B5" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+    </row>
+    <row r="6" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="25">
+        <v>6</v>
+      </c>
+      <c r="B6" s="52" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+    </row>
+    <row r="7" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="25">
+        <v>7</v>
+      </c>
+      <c r="B7" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+    </row>
+    <row r="8" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="25">
+        <v>8</v>
+      </c>
+      <c r="B8" s="52" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+    </row>
+    <row r="9" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="25">
+        <v>9</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+    </row>
+    <row r="10" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="25">
+        <v>10</v>
+      </c>
+      <c r="B10" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+    </row>
+    <row r="11" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="25">
+        <v>11</v>
+      </c>
+      <c r="B11" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+    </row>
+    <row r="12" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="25">
+        <v>12</v>
+      </c>
+      <c r="B12" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+    </row>
+    <row r="13" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="25">
         <v>13</v>
       </c>
-      <c r="B17" s="52" t="s">
+      <c r="B13" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+    </row>
+    <row r="14" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="25">
         <v>14</v>
       </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="52"/>
-    </row>
-    <row r="18" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A18" s="26">
+      <c r="B14" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+    </row>
+    <row r="15" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="25">
+        <v>15</v>
+      </c>
+      <c r="B15" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+    </row>
+    <row r="16" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="25">
+        <v>16</v>
+      </c>
+      <c r="B16" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF15DEF4-8933-48F5-A839-F1CFBCA8C220}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="27">
+        <v>1</v>
+      </c>
+      <c r="B1" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="55"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="27">
+        <v>2</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="55"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="27">
+        <v>3</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="55"/>
+    </row>
+    <row r="4" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="27">
+        <v>4</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="27">
+        <v>5</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="55"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="27">
+        <v>6</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="55"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="27">
+        <v>7</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="55"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <v>8</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="55"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="27">
+        <v>9</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="55"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="27">
+        <v>10</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="55"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="27">
+        <v>11</v>
+      </c>
+      <c r="B11" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="55"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>12</v>
+      </c>
+      <c r="B12" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="55"/>
+    </row>
+    <row r="13" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="27">
+        <v>13</v>
+      </c>
+      <c r="B13" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="55"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="27">
         <v>14</v>
       </c>
-      <c r="B18" s="52" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="52"/>
-    </row>
-    <row r="19" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A19" s="26">
+      <c r="B14" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="55"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="27">
         <v>15</v>
       </c>
-      <c r="B19" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
-    </row>
-    <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A20" s="26">
+      <c r="B15" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="55"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="27">
         <v>16</v>
       </c>
-      <c r="B20" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-    </row>
-    <row r="24" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B24" s="34" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A26" s="26">
+      <c r="B16" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="27">
+        <v>17</v>
+      </c>
+      <c r="B17" s="56" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="27">
+        <v>18</v>
+      </c>
+      <c r="B18" s="56" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B11:F11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12E8C188-DEA5-4CD2-A4A0-69C5A7F46AE5}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="27">
         <v>1</v>
       </c>
-      <c r="B26" s="52" t="s">
-        <v>153</v>
-      </c>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="52"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A27" s="26">
+      <c r="B1" s="57" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="59"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="27">
         <v>2</v>
       </c>
-      <c r="B27" s="52" t="s">
-        <v>187</v>
-      </c>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="52"/>
-    </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A28" s="26">
+      <c r="B2" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="59"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="27">
         <v>3</v>
       </c>
-      <c r="B28" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="52"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="52"/>
-    </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A29" s="26">
+      <c r="B3" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="59"/>
+    </row>
+    <row r="4" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="27">
         <v>4</v>
       </c>
-      <c r="B29" s="52" t="s">
-        <v>129</v>
-      </c>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="52"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A30" s="26">
+      <c r="B4" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="52" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A31" s="26">
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="59"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="27">
+        <v>5</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="59"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="27">
         <v>6</v>
       </c>
-      <c r="B31" s="52" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A32" s="26">
+      <c r="B6" s="57" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="59"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="27">
         <v>7</v>
       </c>
-      <c r="B32" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A33" s="26">
+      <c r="B7" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="59"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
         <v>8</v>
       </c>
-      <c r="B33" s="52" t="s">
-        <v>145</v>
-      </c>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A34" s="26">
+      <c r="B8" s="57" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="59"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="27">
         <v>9</v>
       </c>
-      <c r="B34" s="52" t="s">
-        <v>130</v>
-      </c>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-    </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A35" s="26">
+      <c r="B9" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="59"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="27">
         <v>10</v>
       </c>
-      <c r="B35" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="C35" s="52"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-    </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A36" s="26">
+      <c r="B10" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="59"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="27">
         <v>11</v>
       </c>
-      <c r="B36" s="52" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="52"/>
-    </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A37" s="26">
+      <c r="B11" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="62"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
         <v>12</v>
       </c>
-      <c r="B37" s="52" t="s">
-        <v>132</v>
-      </c>
-      <c r="C37" s="52"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
-    </row>
-    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A38" s="26">
+      <c r="B12" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="55"/>
+    </row>
+    <row r="13" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="27">
         <v>13</v>
       </c>
-      <c r="B38" s="52" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-    </row>
-    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A39" s="26">
+      <c r="B13" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="55"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="27">
         <v>14</v>
       </c>
-      <c r="B39" s="52" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" s="52"/>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
-    </row>
-    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A40" s="26">
+      <c r="B14" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="55"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="27">
         <v>15</v>
       </c>
-      <c r="B40" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-    </row>
-    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A41" s="26">
+      <c r="B15" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="55"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="27">
         <v>16</v>
       </c>
-      <c r="B41" s="52" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" s="52"/>
-      <c r="D41" s="52"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="52"/>
+      <c r="B16" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="55"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="27">
+        <v>17</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="55"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B16:F16"/>
+  <mergeCells count="17">
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B7:F7"/>
@@ -3940,517 +4467,17 @@
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B39:F39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF15DEF4-8933-48F5-A839-F1CFBCA8C220}">
-  <dimension ref="A2:F43"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="16384" width="9.140625" style="27"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B2" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="C2" s="29"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="28">
-        <v>1</v>
-      </c>
-      <c r="B4" s="54" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="28">
-        <v>2</v>
-      </c>
-      <c r="B5" s="54" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="28">
-        <v>3</v>
-      </c>
-      <c r="B6" s="54" t="s">
-        <v>142</v>
-      </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="28">
-        <v>4</v>
-      </c>
-      <c r="B7" s="54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="28">
-        <v>5</v>
-      </c>
-      <c r="B8" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="28">
-        <v>6</v>
-      </c>
-      <c r="B9" s="54" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="28">
-        <v>7</v>
-      </c>
-      <c r="B10" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="28">
-        <v>8</v>
-      </c>
-      <c r="B11" s="54" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="28">
-        <v>9</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="28">
-        <v>10</v>
-      </c>
-      <c r="B13" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="28">
-        <v>11</v>
-      </c>
-      <c r="B14" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="28">
-        <v>12</v>
-      </c>
-      <c r="B15" s="54" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="28">
-        <v>13</v>
-      </c>
-      <c r="B16" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="28">
-        <v>14</v>
-      </c>
-      <c r="B17" s="54" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="28">
-        <v>15</v>
-      </c>
-      <c r="B18" s="54" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="28">
-        <v>16</v>
-      </c>
-      <c r="B19" s="54" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="28">
-        <v>17</v>
-      </c>
-      <c r="B20" s="54" t="s">
-        <v>143</v>
-      </c>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="28">
-        <v>18</v>
-      </c>
-      <c r="B21" s="54" t="s">
-        <v>141</v>
-      </c>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-    </row>
-    <row r="25" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B25" s="29" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="28">
-        <v>1</v>
-      </c>
-      <c r="B27" s="55" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="28">
-        <v>2</v>
-      </c>
-      <c r="B28" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="28">
-        <v>3</v>
-      </c>
-      <c r="B29" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" s="56"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="28">
-        <v>4</v>
-      </c>
-      <c r="B30" s="55" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="28">
-        <v>5</v>
-      </c>
-      <c r="B31" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="56"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="56"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="28">
-        <v>6</v>
-      </c>
-      <c r="B32" s="55" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" s="56"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="56"/>
-      <c r="F32" s="56"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="28">
-        <v>7</v>
-      </c>
-      <c r="B33" s="55" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" s="56"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="28">
-        <v>8</v>
-      </c>
-      <c r="B34" s="55" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="56"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="28">
-        <v>9</v>
-      </c>
-      <c r="B35" s="55" t="s">
-        <v>81</v>
-      </c>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="28">
-        <v>10</v>
-      </c>
-      <c r="B36" s="55" t="s">
-        <v>155</v>
-      </c>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="56"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="28">
-        <v>11</v>
-      </c>
-      <c r="B37" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="54"/>
-      <c r="D37" s="54"/>
-      <c r="E37" s="54"/>
-      <c r="F37" s="54"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="28">
-        <v>12</v>
-      </c>
-      <c r="B38" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="54"/>
-      <c r="D38" s="54"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="54"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="28">
-        <v>13</v>
-      </c>
-      <c r="B39" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" s="54"/>
-      <c r="D39" s="54"/>
-      <c r="E39" s="54"/>
-      <c r="F39" s="54"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="28">
-        <v>14</v>
-      </c>
-      <c r="B40" s="53" t="s">
-        <v>83</v>
-      </c>
-      <c r="C40" s="54"/>
-      <c r="D40" s="54"/>
-      <c r="E40" s="54"/>
-      <c r="F40" s="54"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="28">
-        <v>15</v>
-      </c>
-      <c r="B41" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="C41" s="54"/>
-      <c r="D41" s="54"/>
-      <c r="E41" s="54"/>
-      <c r="F41" s="54"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="28">
-        <v>16</v>
-      </c>
-      <c r="B42" s="53" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="54"/>
-      <c r="D42" s="54"/>
-      <c r="E42" s="54"/>
-      <c r="F42" s="54"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="28">
-        <v>17</v>
-      </c>
-      <c r="B43" s="53" t="s">
-        <v>176</v>
-      </c>
-      <c r="C43" s="54"/>
-      <c r="D43" s="54"/>
-      <c r="E43" s="54"/>
-      <c r="F43" s="54"/>
-    </row>
-  </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B43:F43"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4469,16 +4496,16 @@
   <sheetData>
     <row r="1" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8"/>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="66" t="s">
         <v>137</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
@@ -4505,16 +4532,16 @@
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -4535,16 +4562,16 @@
       <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="63" t="s">
         <v>146</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="59"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="65"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -4556,16 +4583,16 @@
       <c r="A4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="59"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="65"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -4577,16 +4604,16 @@
       <c r="A5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="63" t="s">
         <v>150</v>
       </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="59"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="65"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -4598,76 +4625,76 @@
       <c r="A6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="59"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="65"/>
     </row>
     <row r="7" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <v>5</v>
       </c>
-      <c r="B7" s="57" t="s">
+      <c r="B7" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="59"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="65"/>
     </row>
     <row r="8" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="11">
         <v>6</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="59"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="65"/>
     </row>
     <row r="9" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>7</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="59"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="65"/>
     </row>
     <row r="10" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11">
         <v>8</v>
       </c>
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="63" t="s">
         <v>156</v>
       </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="59"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="65"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -4679,16 +4706,16 @@
       <c r="A11" s="11">
         <v>9</v>
       </c>
-      <c r="B11" s="57" t="s">
+      <c r="B11" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="59"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="65"/>
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11"/>
@@ -4700,16 +4727,16 @@
       <c r="A12" s="11">
         <v>10</v>
       </c>
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="59"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="65"/>
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12"/>
@@ -4720,16 +4747,16 @@
       <c r="A13" s="11">
         <v>11</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="63" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="59"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="65"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
@@ -4741,16 +4768,16 @@
       <c r="A14" s="11">
         <v>12</v>
       </c>
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="63" t="s">
         <v>151</v>
       </c>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="59"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="65"/>
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14"/>
@@ -4782,862 +4809,748 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:AI49"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" style="7" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" style="1" customWidth="1"/>
-    <col min="3" max="8" width="10.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" style="1" customWidth="1"/>
-    <col min="10" max="14" width="0.140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="0.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.85546875" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="8" width="10.42578125" customWidth="1"/>
+    <col min="9" max="9" width="9.28515625" customWidth="1"/>
+    <col min="10" max="14" width="0.140625" customWidth="1"/>
+    <col min="15" max="15" width="0.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="8"/>
-      <c r="B1" s="60" t="s">
+    <row r="1" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="32"/>
+      <c r="B1" s="70" t="s">
         <v>136</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-    </row>
-    <row r="2" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="71"/>
+    </row>
+    <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="65"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
-      <c r="AC2" s="1"/>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
-      <c r="AF2" s="1"/>
-      <c r="AG2" s="1"/>
-      <c r="AH2" s="1"/>
-      <c r="AI2" s="1"/>
-    </row>
-    <row r="3" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12">
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="69"/>
+    </row>
+    <row r="3" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="33">
         <v>1</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="64"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="3"/>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3"/>
-    </row>
-    <row r="4" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="12">
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="69"/>
+    </row>
+    <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="33">
         <v>2</v>
       </c>
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="64"/>
-    </row>
-    <row r="5" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12">
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="69"/>
+    </row>
+    <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="33">
         <v>3</v>
       </c>
-      <c r="B5" s="62" t="s">
+      <c r="B5" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="64"/>
-    </row>
-    <row r="6" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="12">
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="69"/>
+    </row>
+    <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="33">
         <v>4</v>
       </c>
-      <c r="B6" s="62" t="s">
+      <c r="B6" s="68" t="s">
         <v>157</v>
       </c>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="64"/>
-    </row>
-    <row r="7" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12">
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="69"/>
+    </row>
+    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="33">
         <v>5</v>
       </c>
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="64"/>
-    </row>
-    <row r="8" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12">
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="69"/>
+    </row>
+    <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="33">
         <v>6</v>
       </c>
-      <c r="B8" s="62" t="s">
+      <c r="B8" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12">
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="69"/>
+    </row>
+    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="33">
         <v>7</v>
       </c>
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-    </row>
-    <row r="10" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12">
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="69"/>
+    </row>
+    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="33">
         <v>8</v>
       </c>
-      <c r="B10" s="62" t="s">
+      <c r="B10" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="64"/>
-    </row>
-    <row r="11" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12">
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="69"/>
+    </row>
+    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="33">
         <v>9</v>
       </c>
-      <c r="B11" s="62" t="s">
+      <c r="B11" s="68" t="s">
         <v>149</v>
       </c>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12">
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="69"/>
+    </row>
+    <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="33">
         <v>10</v>
       </c>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="12">
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="69"/>
+    </row>
+    <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="33">
         <v>11</v>
       </c>
-      <c r="B13" s="62" t="s">
+      <c r="B13" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="63"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="64"/>
-    </row>
-    <row r="14" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="12">
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="69"/>
+    </row>
+    <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="33">
         <v>12</v>
       </c>
-      <c r="B14" s="62" t="s">
+      <c r="B14" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="C14" s="63"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="63"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="64"/>
-    </row>
-    <row r="15" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12">
+      <c r="C14" s="68"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="69"/>
+    </row>
+    <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="33">
         <v>13</v>
       </c>
-      <c r="B15" s="62" t="s">
+      <c r="B15" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="63"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="64"/>
-    </row>
-    <row r="16" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="12">
+      <c r="C15" s="68"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="69"/>
+    </row>
+    <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="33">
         <v>14</v>
       </c>
-      <c r="B16" s="62" t="s">
+      <c r="B16" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="63"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="63"/>
-      <c r="G16" s="63"/>
-      <c r="H16" s="63"/>
-      <c r="I16" s="64"/>
-    </row>
-    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12">
+      <c r="C16" s="68"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="69"/>
+    </row>
+    <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="33">
         <v>15</v>
       </c>
-      <c r="B17" s="62" t="s">
+      <c r="B17" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="63"/>
-      <c r="I17" s="64"/>
-    </row>
-    <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12">
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="69"/>
+    </row>
+    <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="33">
         <v>16</v>
       </c>
-      <c r="B18" s="62" t="s">
+      <c r="B18" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="64"/>
-    </row>
-    <row r="19" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12">
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="69"/>
+    </row>
+    <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="33">
         <v>17</v>
       </c>
-      <c r="B19" s="62" t="s">
+      <c r="B19" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="64"/>
-    </row>
-    <row r="20" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12">
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="69"/>
+    </row>
+    <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="33">
         <v>18</v>
       </c>
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="68" t="s">
         <v>101</v>
       </c>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="64"/>
-    </row>
-    <row r="21" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12">
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="69"/>
+    </row>
+    <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="33">
         <v>19</v>
       </c>
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="63"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="63"/>
-      <c r="F21" s="63"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="63"/>
-      <c r="I21" s="64"/>
-    </row>
-    <row r="22" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12">
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="69"/>
+    </row>
+    <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="33">
         <v>20</v>
       </c>
-      <c r="B22" s="62" t="s">
+      <c r="B22" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="63"/>
-      <c r="H22" s="63"/>
-      <c r="I22" s="64"/>
-    </row>
-    <row r="23" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12">
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="69"/>
+    </row>
+    <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="33">
         <v>21</v>
       </c>
-      <c r="B23" s="62" t="s">
+      <c r="B23" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="64"/>
-    </row>
-    <row r="24" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12">
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="69"/>
+    </row>
+    <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="33">
         <v>22</v>
       </c>
-      <c r="B24" s="62" t="s">
+      <c r="B24" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12">
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="69"/>
+    </row>
+    <row r="25" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="33">
         <v>23</v>
       </c>
-      <c r="B25" s="62" t="s">
+      <c r="B25" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="C25" s="63"/>
-      <c r="D25" s="63"/>
-      <c r="E25" s="63"/>
-      <c r="F25" s="63"/>
-      <c r="G25" s="63"/>
-      <c r="H25" s="63"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="12">
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="69"/>
+    </row>
+    <row r="26" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="33">
         <v>24</v>
       </c>
-      <c r="B26" s="62" t="s">
+      <c r="B26" s="68" t="s">
         <v>107</v>
       </c>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="63"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="63"/>
-      <c r="I26" s="64"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="12">
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="69"/>
+    </row>
+    <row r="27" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="33">
         <v>25</v>
       </c>
-      <c r="B27" s="62" t="s">
+      <c r="B27" s="68" t="s">
         <v>133</v>
       </c>
-      <c r="C27" s="63"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="63"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="64"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="12">
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="69"/>
+    </row>
+    <row r="28" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="33">
         <v>26</v>
       </c>
-      <c r="B28" s="62" t="s">
+      <c r="B28" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="C28" s="63"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="63"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="12">
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="69"/>
+    </row>
+    <row r="29" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="33">
         <v>27</v>
       </c>
-      <c r="B29" s="62" t="s">
+      <c r="B29" s="68" t="s">
         <v>109</v>
       </c>
-      <c r="C29" s="63"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="64"/>
-    </row>
-    <row r="30" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="12">
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="69"/>
+    </row>
+    <row r="30" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="33">
         <v>28</v>
       </c>
-      <c r="B30" s="62" t="s">
+      <c r="B30" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="C30" s="63"/>
-      <c r="D30" s="63"/>
-      <c r="E30" s="63"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="63"/>
-      <c r="H30" s="63"/>
-      <c r="I30" s="64"/>
-    </row>
-    <row r="31" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="12">
+      <c r="C30" s="68"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="68"/>
+      <c r="F30" s="68"/>
+      <c r="G30" s="68"/>
+      <c r="H30" s="68"/>
+      <c r="I30" s="69"/>
+    </row>
+    <row r="31" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="33">
         <v>29</v>
       </c>
-      <c r="B31" s="62" t="s">
+      <c r="B31" s="68" t="s">
         <v>134</v>
       </c>
-      <c r="C31" s="63"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="63"/>
-      <c r="F31" s="63"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="64"/>
-    </row>
-    <row r="32" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="12">
+      <c r="C31" s="68"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="68"/>
+      <c r="H31" s="68"/>
+      <c r="I31" s="69"/>
+    </row>
+    <row r="32" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="33">
         <v>30</v>
       </c>
-      <c r="B32" s="62" t="s">
+      <c r="B32" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="C32" s="63"/>
-      <c r="D32" s="63"/>
-      <c r="E32" s="63"/>
-      <c r="F32" s="63"/>
-      <c r="G32" s="63"/>
-      <c r="H32" s="63"/>
-      <c r="I32" s="64"/>
-    </row>
-    <row r="33" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="12">
+      <c r="C32" s="68"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="68"/>
+      <c r="H32" s="68"/>
+      <c r="I32" s="69"/>
+    </row>
+    <row r="33" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="33">
         <v>31</v>
       </c>
-      <c r="B33" s="62" t="s">
+      <c r="B33" s="68" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="63"/>
-      <c r="D33" s="63"/>
-      <c r="E33" s="63"/>
-      <c r="F33" s="63"/>
-      <c r="G33" s="63"/>
-      <c r="H33" s="63"/>
-      <c r="I33" s="64"/>
-    </row>
-    <row r="34" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="12">
+      <c r="C33" s="68"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="68"/>
+      <c r="F33" s="68"/>
+      <c r="G33" s="68"/>
+      <c r="H33" s="68"/>
+      <c r="I33" s="69"/>
+    </row>
+    <row r="34" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="33">
         <v>32</v>
       </c>
-      <c r="B34" s="62" t="s">
+      <c r="B34" s="68" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="63"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="63"/>
-      <c r="F34" s="63"/>
-      <c r="G34" s="63"/>
-      <c r="H34" s="63"/>
-      <c r="I34" s="64"/>
-    </row>
-    <row r="35" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="12">
+      <c r="C34" s="68"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="68"/>
+      <c r="G34" s="68"/>
+      <c r="H34" s="68"/>
+      <c r="I34" s="69"/>
+    </row>
+    <row r="35" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="33">
         <v>33</v>
       </c>
-      <c r="B35" s="62" t="s">
+      <c r="B35" s="68" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="63"/>
-      <c r="D35" s="63"/>
-      <c r="E35" s="63"/>
-      <c r="F35" s="63"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="64"/>
-    </row>
-    <row r="36" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="12">
+      <c r="C35" s="68"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="68"/>
+      <c r="H35" s="68"/>
+      <c r="I35" s="69"/>
+    </row>
+    <row r="36" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="33">
         <v>34</v>
       </c>
-      <c r="B36" s="62" t="s">
+      <c r="B36" s="68" t="s">
         <v>115</v>
       </c>
-      <c r="C36" s="63"/>
-      <c r="D36" s="63"/>
-      <c r="E36" s="63"/>
-      <c r="F36" s="63"/>
-      <c r="G36" s="63"/>
-      <c r="H36" s="63"/>
-      <c r="I36" s="64"/>
-    </row>
-    <row r="37" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="12">
+      <c r="C36" s="68"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="68"/>
+      <c r="H36" s="68"/>
+      <c r="I36" s="69"/>
+    </row>
+    <row r="37" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="33">
         <v>35</v>
       </c>
-      <c r="B37" s="62" t="s">
+      <c r="B37" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="C37" s="63"/>
-      <c r="D37" s="63"/>
-      <c r="E37" s="63"/>
-      <c r="F37" s="63"/>
-      <c r="G37" s="63"/>
-      <c r="H37" s="63"/>
-      <c r="I37" s="64"/>
-    </row>
-    <row r="38" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="12">
+      <c r="C37" s="68"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="68"/>
+      <c r="H37" s="68"/>
+      <c r="I37" s="69"/>
+    </row>
+    <row r="38" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="33">
         <v>36</v>
       </c>
-      <c r="B38" s="62" t="s">
+      <c r="B38" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="C38" s="63"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="63"/>
-      <c r="F38" s="63"/>
-      <c r="G38" s="63"/>
-      <c r="H38" s="63"/>
-      <c r="I38" s="64"/>
-    </row>
-    <row r="39" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="12">
+      <c r="C38" s="68"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="68"/>
+      <c r="H38" s="68"/>
+      <c r="I38" s="69"/>
+    </row>
+    <row r="39" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="33">
         <v>37</v>
       </c>
-      <c r="B39" s="72" t="s">
+      <c r="B39" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="C39" s="63"/>
-      <c r="D39" s="63"/>
-      <c r="E39" s="63"/>
-      <c r="F39" s="63"/>
-      <c r="G39" s="63"/>
-      <c r="H39" s="63"/>
-      <c r="I39" s="64"/>
-      <c r="J39" s="73"/>
-      <c r="K39" s="73"/>
-      <c r="L39" s="73"/>
-      <c r="M39"/>
-      <c r="N39"/>
-      <c r="O39"/>
-    </row>
-    <row r="40" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="12">
+      <c r="C39" s="68"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="68"/>
+      <c r="G39" s="68"/>
+      <c r="H39" s="68"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="72"/>
+      <c r="K39" s="72"/>
+      <c r="L39" s="72"/>
+    </row>
+    <row r="40" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="33">
         <v>38</v>
       </c>
-      <c r="B40" s="74" t="s">
+      <c r="B40" s="68" t="s">
         <v>119</v>
       </c>
-      <c r="C40" s="75"/>
-      <c r="D40" s="75"/>
-      <c r="E40" s="75"/>
-      <c r="F40" s="75"/>
-      <c r="G40" s="75"/>
-      <c r="H40" s="75"/>
-      <c r="I40" s="76"/>
-    </row>
-    <row r="41" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="12">
+      <c r="C40" s="68"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="68"/>
+      <c r="H40" s="68"/>
+      <c r="I40" s="69"/>
+    </row>
+    <row r="41" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="33">
         <v>39</v>
       </c>
-      <c r="B41" s="69" t="s">
+      <c r="B41" s="68" t="s">
         <v>120</v>
       </c>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="71"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5"/>
-      <c r="U41"/>
-      <c r="V41"/>
-      <c r="W41"/>
-      <c r="X41"/>
-      <c r="Y41"/>
-      <c r="Z41"/>
-      <c r="AA41"/>
-      <c r="AB41"/>
-      <c r="AC41"/>
-      <c r="AD41"/>
-      <c r="AE41"/>
-      <c r="AF41"/>
-      <c r="AG41"/>
-      <c r="AH41"/>
-      <c r="AI41"/>
-    </row>
-    <row r="42" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="12">
+      <c r="C41" s="68"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
+      <c r="H41" s="68"/>
+      <c r="I41" s="69"/>
+    </row>
+    <row r="42" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="33">
         <v>40</v>
       </c>
-      <c r="B42" s="66" t="s">
+      <c r="B42" s="68" t="s">
         <v>159</v>
       </c>
-      <c r="C42" s="67"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="67"/>
-      <c r="H42" s="67"/>
-      <c r="I42" s="68"/>
-    </row>
-    <row r="43" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="12">
+      <c r="C42" s="68"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="68"/>
+      <c r="H42" s="68"/>
+      <c r="I42" s="69"/>
+    </row>
+    <row r="43" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="33">
         <v>41</v>
       </c>
-      <c r="B43" s="66" t="s">
+      <c r="B43" s="68" t="s">
         <v>160</v>
       </c>
-      <c r="C43" s="67"/>
-      <c r="D43" s="67"/>
-      <c r="E43" s="67"/>
-      <c r="F43" s="67"/>
-      <c r="G43" s="67"/>
-      <c r="H43" s="67"/>
-      <c r="I43" s="68"/>
-    </row>
-    <row r="44" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="12">
+      <c r="C43" s="68"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="68"/>
+      <c r="F43" s="68"/>
+      <c r="G43" s="68"/>
+      <c r="H43" s="68"/>
+      <c r="I43" s="69"/>
+    </row>
+    <row r="44" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="33">
         <v>42</v>
       </c>
-      <c r="B44" s="66" t="s">
+      <c r="B44" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="C44" s="67"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="67"/>
-      <c r="F44" s="67"/>
-      <c r="G44" s="67"/>
-      <c r="H44" s="67"/>
-      <c r="I44" s="68"/>
-    </row>
-    <row r="45" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="12">
+      <c r="C44" s="68"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="68"/>
+      <c r="F44" s="68"/>
+      <c r="G44" s="68"/>
+      <c r="H44" s="68"/>
+      <c r="I44" s="69"/>
+    </row>
+    <row r="45" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="33">
         <v>43</v>
       </c>
-      <c r="B45" s="66" t="s">
+      <c r="B45" s="68" t="s">
         <v>162</v>
       </c>
-      <c r="C45" s="67"/>
-      <c r="D45" s="67"/>
-      <c r="E45" s="67"/>
-      <c r="F45" s="67"/>
-      <c r="G45" s="67"/>
-      <c r="H45" s="67"/>
-      <c r="I45" s="68"/>
-    </row>
-    <row r="46" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="12">
+      <c r="C45" s="68"/>
+      <c r="D45" s="68"/>
+      <c r="E45" s="68"/>
+      <c r="F45" s="68"/>
+      <c r="G45" s="68"/>
+      <c r="H45" s="68"/>
+      <c r="I45" s="69"/>
+    </row>
+    <row r="46" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="33">
         <v>44</v>
       </c>
-      <c r="B46" s="66" t="s">
+      <c r="B46" s="68" t="s">
         <v>163</v>
       </c>
-      <c r="C46" s="67"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="67"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="67"/>
-      <c r="H46" s="67"/>
-      <c r="I46" s="68"/>
-    </row>
-    <row r="47" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="12">
+      <c r="C46" s="68"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="68"/>
+      <c r="F46" s="68"/>
+      <c r="G46" s="68"/>
+      <c r="H46" s="68"/>
+      <c r="I46" s="69"/>
+    </row>
+    <row r="47" spans="1:12" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="34">
         <v>45</v>
       </c>
-      <c r="B47" s="66" t="s">
+      <c r="B47" s="73" t="s">
         <v>164</v>
       </c>
-      <c r="C47" s="67"/>
-      <c r="D47" s="67"/>
-      <c r="E47" s="67"/>
-      <c r="F47" s="67"/>
-      <c r="G47" s="67"/>
-      <c r="H47" s="67"/>
-      <c r="I47" s="68"/>
-    </row>
-    <row r="48" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="69"/>
-      <c r="C48" s="70"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
-      <c r="I48" s="71"/>
+      <c r="C47" s="73"/>
+      <c r="D47" s="73"/>
+      <c r="E47" s="73"/>
+      <c r="F47" s="73"/>
+      <c r="G47" s="73"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="74"/>
+    </row>
+    <row r="48" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="72"/>
+      <c r="C48" s="72"/>
+      <c r="D48" s="72"/>
+      <c r="E48" s="72"/>
+      <c r="F48" s="72"/>
+      <c r="G48" s="72"/>
+      <c r="H48" s="72"/>
+      <c r="I48" s="72"/>
     </row>
     <row r="49" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="69"/>
-      <c r="C49" s="70"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
-      <c r="F49" s="70"/>
-      <c r="G49" s="70"/>
-      <c r="H49" s="70"/>
-      <c r="I49" s="71"/>
+      <c r="B49" s="72"/>
+      <c r="C49" s="72"/>
+      <c r="D49" s="72"/>
+      <c r="E49" s="72"/>
+      <c r="F49" s="72"/>
+      <c r="G49" s="72"/>
+      <c r="H49" s="72"/>
+      <c r="I49" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="50">
@@ -5700,13 +5613,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:AI23"/>
+  <dimension ref="A1:AI21"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="7" customWidth="1"/>
@@ -5717,94 +5630,91 @@
     <col min="15" max="15" width="0.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7"/>
-      <c r="B1"/>
-      <c r="C1"/>
-      <c r="D1"/>
-      <c r="E1"/>
-      <c r="F1"/>
-      <c r="G1"/>
-      <c r="H1"/>
-      <c r="I1"/>
-      <c r="J1"/>
-      <c r="K1"/>
-      <c r="L1"/>
-      <c r="M1"/>
-      <c r="N1"/>
-      <c r="O1"/>
+    <row r="1" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="8"/>
+      <c r="B1" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="U1"/>
+      <c r="V1"/>
+      <c r="W1"/>
+      <c r="X1"/>
+      <c r="Y1"/>
+      <c r="Z1"/>
+      <c r="AA1"/>
+      <c r="AB1"/>
+      <c r="AC1"/>
+      <c r="AD1"/>
+      <c r="AE1"/>
+      <c r="AF1"/>
+      <c r="AG1"/>
+      <c r="AH1"/>
+      <c r="AI1"/>
     </row>
     <row r="2" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-    </row>
-    <row r="3" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="8"/>
-      <c r="B3" s="77" t="s">
-        <v>135</v>
-      </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="76"/>
+    </row>
+    <row r="3" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="10">
+        <v>1</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
       <c r="I3" s="77"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="U3"/>
-      <c r="V3"/>
-      <c r="W3"/>
-      <c r="X3"/>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3"/>
-      <c r="AB3"/>
-      <c r="AC3"/>
-      <c r="AD3"/>
-      <c r="AE3"/>
-      <c r="AF3"/>
-      <c r="AG3"/>
-      <c r="AH3"/>
-      <c r="AI3"/>
     </row>
     <row r="4" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="65"/>
+      <c r="A4" s="10">
+        <v>2</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="77"/>
     </row>
     <row r="5" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="C5" s="38"/>
       <c r="D5" s="38"/>
@@ -5812,14 +5722,14 @@
       <c r="F5" s="38"/>
       <c r="G5" s="38"/>
       <c r="H5" s="38"/>
-      <c r="I5" s="78"/>
+      <c r="I5" s="77"/>
     </row>
     <row r="6" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="C6" s="38"/>
       <c r="D6" s="38"/>
@@ -5827,14 +5737,14 @@
       <c r="F6" s="38"/>
       <c r="G6" s="38"/>
       <c r="H6" s="38"/>
-      <c r="I6" s="78"/>
+      <c r="I6" s="77"/>
     </row>
     <row r="7" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>34</v>
+        <v>158</v>
       </c>
       <c r="C7" s="38"/>
       <c r="D7" s="38"/>
@@ -5842,14 +5752,14 @@
       <c r="F7" s="38"/>
       <c r="G7" s="38"/>
       <c r="H7" s="38"/>
-      <c r="I7" s="78"/>
+      <c r="I7" s="77"/>
     </row>
     <row r="8" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="C8" s="38"/>
       <c r="D8" s="38"/>
@@ -5857,14 +5767,14 @@
       <c r="F8" s="38"/>
       <c r="G8" s="38"/>
       <c r="H8" s="38"/>
-      <c r="I8" s="78"/>
+      <c r="I8" s="77"/>
     </row>
     <row r="9" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>158</v>
+        <v>39</v>
       </c>
       <c r="C9" s="38"/>
       <c r="D9" s="38"/>
@@ -5872,14 +5782,14 @@
       <c r="F9" s="38"/>
       <c r="G9" s="38"/>
       <c r="H9" s="38"/>
-      <c r="I9" s="78"/>
+      <c r="I9" s="77"/>
     </row>
     <row r="10" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C10" s="38"/>
       <c r="D10" s="38"/>
@@ -5887,14 +5797,14 @@
       <c r="F10" s="38"/>
       <c r="G10" s="38"/>
       <c r="H10" s="38"/>
-      <c r="I10" s="78"/>
+      <c r="I10" s="77"/>
     </row>
     <row r="11" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="38"/>
       <c r="D11" s="38"/>
@@ -5902,14 +5812,14 @@
       <c r="F11" s="38"/>
       <c r="G11" s="38"/>
       <c r="H11" s="38"/>
-      <c r="I11" s="78"/>
+      <c r="I11" s="77"/>
     </row>
     <row r="12" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="C12" s="38"/>
       <c r="D12" s="38"/>
@@ -5917,14 +5827,14 @@
       <c r="F12" s="38"/>
       <c r="G12" s="38"/>
       <c r="H12" s="38"/>
-      <c r="I12" s="78"/>
+      <c r="I12" s="77"/>
     </row>
     <row r="13" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C13" s="38"/>
       <c r="D13" s="38"/>
@@ -5932,14 +5842,14 @@
       <c r="F13" s="38"/>
       <c r="G13" s="38"/>
       <c r="H13" s="38"/>
-      <c r="I13" s="78"/>
+      <c r="I13" s="77"/>
     </row>
     <row r="14" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C14" s="38"/>
       <c r="D14" s="38"/>
@@ -5947,14 +5857,20 @@
       <c r="F14" s="38"/>
       <c r="G14" s="38"/>
       <c r="H14" s="38"/>
-      <c r="I14" s="78"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
     </row>
     <row r="15" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C15" s="38"/>
       <c r="D15" s="38"/>
@@ -5962,14 +5878,35 @@
       <c r="F15" s="38"/>
       <c r="G15" s="38"/>
       <c r="H15" s="38"/>
-      <c r="I15" s="78"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="3"/>
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="3"/>
+      <c r="AH15" s="3"/>
+      <c r="AI15" s="3"/>
     </row>
     <row r="16" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="C16" s="38"/>
       <c r="D16" s="38"/>
@@ -5977,20 +5914,35 @@
       <c r="F16" s="38"/>
       <c r="G16" s="38"/>
       <c r="H16" s="38"/>
-      <c r="I16" s="78"/>
+      <c r="I16" s="77"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="C17" s="38"/>
       <c r="D17" s="38"/>
@@ -5998,13 +5950,13 @@
       <c r="F17" s="38"/>
       <c r="G17" s="38"/>
       <c r="H17" s="38"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -6021,12 +5973,12 @@
       <c r="AH17" s="3"/>
       <c r="AI17" s="3"/>
     </row>
-    <row r="18" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="C18" s="38"/>
       <c r="D18" s="38"/>
@@ -6034,35 +5986,35 @@
       <c r="F18" s="38"/>
       <c r="G18" s="38"/>
       <c r="H18" s="38"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="3"/>
-      <c r="AB18" s="3"/>
-      <c r="AC18" s="3"/>
-      <c r="AD18" s="3"/>
-      <c r="AE18" s="3"/>
-      <c r="AF18" s="3"/>
-      <c r="AG18" s="3"/>
-      <c r="AH18" s="3"/>
-      <c r="AI18" s="3"/>
+      <c r="I18" s="77"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="4"/>
+      <c r="AA18" s="4"/>
+      <c r="AB18" s="4"/>
+      <c r="AC18" s="4"/>
+      <c r="AD18" s="4"/>
+      <c r="AE18" s="4"/>
+      <c r="AF18" s="4"/>
+      <c r="AG18" s="4"/>
+      <c r="AH18" s="4"/>
+      <c r="AI18" s="4"/>
     </row>
     <row r="19" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
@@ -6070,35 +6022,35 @@
       <c r="F19" s="38"/>
       <c r="G19" s="38"/>
       <c r="H19" s="38"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
-      <c r="AB19" s="3"/>
-      <c r="AC19" s="3"/>
-      <c r="AD19" s="3"/>
-      <c r="AE19" s="3"/>
-      <c r="AF19" s="3"/>
-      <c r="AG19" s="3"/>
-      <c r="AH19" s="3"/>
-      <c r="AI19" s="3"/>
-    </row>
-    <row r="20" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I19" s="77"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4"/>
+      <c r="Z19" s="4"/>
+      <c r="AA19" s="4"/>
+      <c r="AB19" s="4"/>
+      <c r="AC19" s="4"/>
+      <c r="AD19" s="4"/>
+      <c r="AE19" s="4"/>
+      <c r="AF19" s="4"/>
+      <c r="AG19" s="4"/>
+      <c r="AH19" s="4"/>
+      <c r="AI19" s="4"/>
+    </row>
+    <row r="20" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>148</v>
+        <v>41</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="38"/>
@@ -6106,13 +6058,13 @@
       <c r="F20" s="38"/>
       <c r="G20" s="38"/>
       <c r="H20" s="38"/>
-      <c r="I20" s="78"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
       <c r="U20" s="4"/>
       <c r="V20" s="4"/>
       <c r="W20" s="4"/>
@@ -6129,12 +6081,12 @@
       <c r="AH20" s="4"/>
       <c r="AI20" s="4"/>
     </row>
-    <row r="21" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10">
-        <v>17</v>
+    <row r="21" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="7">
+        <v>19</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="C21" s="38"/>
       <c r="D21" s="38"/>
@@ -6142,92 +6094,22 @@
       <c r="F21" s="38"/>
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
-      <c r="I21" s="78"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="4"/>
-      <c r="W21" s="4"/>
-      <c r="X21" s="4"/>
-      <c r="Y21" s="4"/>
-      <c r="Z21" s="4"/>
-      <c r="AA21" s="4"/>
-      <c r="AB21" s="4"/>
-      <c r="AC21" s="4"/>
-      <c r="AD21" s="4"/>
-      <c r="AE21" s="4"/>
-      <c r="AF21" s="4"/>
-      <c r="AG21" s="4"/>
-      <c r="AH21" s="4"/>
-      <c r="AI21" s="4"/>
-    </row>
-    <row r="22" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10">
-        <v>18</v>
-      </c>
-      <c r="B22" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="U22" s="4"/>
-      <c r="V22" s="4"/>
-      <c r="W22" s="4"/>
-      <c r="X22" s="4"/>
-      <c r="Y22" s="4"/>
-      <c r="Z22" s="4"/>
-      <c r="AA22" s="4"/>
-      <c r="AB22" s="4"/>
-      <c r="AC22" s="4"/>
-      <c r="AD22" s="4"/>
-      <c r="AE22" s="4"/>
-      <c r="AF22" s="4"/>
-      <c r="AG22" s="4"/>
-      <c r="AH22" s="4"/>
-      <c r="AI22" s="4"/>
-    </row>
-    <row r="23" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="7">
-        <v>19</v>
-      </c>
-      <c r="B23" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="78"/>
+      <c r="I21" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="B16:I16"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="B18:I18"/>
     <mergeCell ref="B19:I19"/>
     <mergeCell ref="B20:I20"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B14:I14"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B16:I16"/>
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B7:I7"/>
@@ -6237,21 +6119,16 @@
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="B14:I14"/>
-    <mergeCell ref="B15:I15"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Arial,normal"&amp;8&amp;P из &amp;N</oddFooter>
   </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="2" max="11" man="1"/>
-  </rowBreaks>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -6270,16 +6147,16 @@
   <sheetData>
     <row r="1" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="66" t="s">
         <v>139</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
@@ -6315,7 +6192,7 @@
       <c r="F2" s="51"/>
       <c r="G2" s="51"/>
       <c r="H2" s="51"/>
-      <c r="I2" s="65"/>
+      <c r="I2" s="76"/>
     </row>
     <row r="3" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10">
@@ -6330,7 +6207,7 @@
       <c r="F3" s="38"/>
       <c r="G3" s="38"/>
       <c r="H3" s="38"/>
-      <c r="I3" s="78"/>
+      <c r="I3" s="77"/>
     </row>
     <row r="4" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
@@ -6345,7 +6222,7 @@
       <c r="F4" s="38"/>
       <c r="G4" s="38"/>
       <c r="H4" s="38"/>
-      <c r="I4" s="78"/>
+      <c r="I4" s="77"/>
     </row>
     <row r="5" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10">
@@ -6360,7 +6237,7 @@
       <c r="F5" s="38"/>
       <c r="G5" s="38"/>
       <c r="H5" s="38"/>
-      <c r="I5" s="78"/>
+      <c r="I5" s="77"/>
     </row>
     <row r="6" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
@@ -6375,7 +6252,7 @@
       <c r="F6" s="38"/>
       <c r="G6" s="38"/>
       <c r="H6" s="38"/>
-      <c r="I6" s="78"/>
+      <c r="I6" s="77"/>
     </row>
     <row r="7" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
@@ -6390,7 +6267,7 @@
       <c r="F7" s="38"/>
       <c r="G7" s="38"/>
       <c r="H7" s="38"/>
-      <c r="I7" s="78"/>
+      <c r="I7" s="77"/>
     </row>
     <row r="8" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
@@ -6405,7 +6282,7 @@
       <c r="F8" s="38"/>
       <c r="G8" s="38"/>
       <c r="H8" s="38"/>
-      <c r="I8" s="78"/>
+      <c r="I8" s="77"/>
     </row>
     <row r="9" spans="1:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
@@ -6420,7 +6297,7 @@
       <c r="F9" s="38"/>
       <c r="G9" s="38"/>
       <c r="H9" s="38"/>
-      <c r="I9" s="78"/>
+      <c r="I9" s="77"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -6456,7 +6333,7 @@
       <c r="F10" s="38"/>
       <c r="G10" s="38"/>
       <c r="H10" s="38"/>
-      <c r="I10" s="78"/>
+      <c r="I10" s="77"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -6492,7 +6369,7 @@
       <c r="F11" s="38"/>
       <c r="G11" s="38"/>
       <c r="H11" s="38"/>
-      <c r="I11" s="78"/>
+      <c r="I11" s="77"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -6528,7 +6405,7 @@
       <c r="F12" s="38"/>
       <c r="G12" s="38"/>
       <c r="H12" s="38"/>
-      <c r="I12" s="78"/>
+      <c r="I12" s="77"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -6564,7 +6441,7 @@
       <c r="F13" s="38"/>
       <c r="G13" s="38"/>
       <c r="H13" s="38"/>
-      <c r="I13" s="78"/>
+      <c r="I13" s="77"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -6600,7 +6477,7 @@
       <c r="F14" s="38"/>
       <c r="G14" s="38"/>
       <c r="H14" s="38"/>
-      <c r="I14" s="78"/>
+      <c r="I14" s="77"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -6636,7 +6513,7 @@
       <c r="F15" s="38"/>
       <c r="G15" s="38"/>
       <c r="H15" s="38"/>
-      <c r="I15" s="78"/>
+      <c r="I15" s="77"/>
     </row>
     <row r="16" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
@@ -6651,7 +6528,7 @@
       <c r="F16" s="38"/>
       <c r="G16" s="38"/>
       <c r="H16" s="38"/>
-      <c r="I16" s="78"/>
+      <c r="I16" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="16">
